--- a/docs/项目功能清单.xlsx
+++ b/docs/项目功能清单.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="405">
   <si>
     <t/>
   </si>
@@ -114,6 +114,99 @@
   </si>
   <si>
     <t>仅本地未发布</t>
+  </si>
+  <si>
+    <t>F18</t>
+  </si>
+  <si>
+    <t>core</t>
+  </si>
+  <si>
+    <t>新法规骨架建档入口</t>
+  </si>
+  <si>
+    <t>部分实现</t>
+  </si>
+  <si>
+    <t>CELEX 或 Title+Part</t>
+  </si>
+  <si>
+    <t>{ok, action, rejected}；缺库时返回 rejected 且不建空库</t>
+  </si>
+  <si>
+    <t>core/law_intake.py</t>
+  </si>
+  <si>
+    <t>依赖未随仓库分发的 sqlite/regulations.sqlite3；缺库时返回 rejected 不建空库；未用真实数据库验证</t>
+  </si>
+  <si>
+    <t>F19</t>
+  </si>
+  <si>
+    <t>scripts</t>
+  </si>
+  <si>
+    <t>官方字段时效核验与过渡期预警</t>
+  </si>
+  <si>
+    <t>法规元数据字段与官方来源时效信息</t>
+  </si>
+  <si>
+    <t>时效核验结果与过渡期预警</t>
+  </si>
+  <si>
+    <t>scripts/check_metadata_freshness.py</t>
+  </si>
+  <si>
+    <t>同样依赖缺失的 sqlite/regulations.sqlite3；官方联网接口比对未执行</t>
+  </si>
+  <si>
+    <t>F20</t>
+  </si>
+  <si>
+    <t>补 units 表 heading 字段</t>
+  </si>
+  <si>
+    <t>units 表中 heading 缺失的记录</t>
+  </si>
+  <si>
+    <t>回填后的 units.heading 字段</t>
+  </si>
+  <si>
+    <t>scripts/backfill_units_heading.py</t>
+  </si>
+  <si>
+    <t>同样依赖缺失的 sqlite/regulations.sqlite3；未用真实数据库验证</t>
+  </si>
+  <si>
+    <t>F21</t>
+  </si>
+  <si>
+    <t>US 长文档 PART 级切片</t>
+  </si>
+  <si>
+    <t>US 超长法规文档</t>
+  </si>
+  <si>
+    <t>按 PART 切分后的文档片段</t>
+  </si>
+  <si>
+    <t>scripts/rechunk_us_fr_long_units.py</t>
+  </si>
+  <si>
+    <t>V10</t>
+  </si>
+  <si>
+    <t>整合 GitHub 远端 9bda0f5（git merge 无冲突，新增 5 文件）</t>
+  </si>
+  <si>
+    <t>四类 py_compile 通过 + 缺库守卫实测 + 合并后 selftest_all 失败数 0</t>
+  </si>
+  <si>
+    <t>Py 编译与缺库行为断言</t>
+  </si>
+  <si>
+    <t>新建档/时效核验完整逻辑与联网接口未验证</t>
   </si>
   <si>
     <r>
@@ -2303,101 +2396,101 @@
   <sheetData>
     <row r="1" spans="1:3" ht="32" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B3" s="7">
         <v>46312</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2413,7 +2506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="J24"/>
+  <dimension ref="J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2430,537 +2523,537 @@
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="5" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="6" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="5" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="6" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="5" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="6" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="5" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>2</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="6" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>4</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="6" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="5" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="6" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="5" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="6" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="5" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="6" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>20</v>
@@ -2969,24 +3062,24 @@
         <v>21</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="5" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>9</v>
@@ -3006,198 +3099,302 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="6" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="5" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="6" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="5" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>190</v>
-      </c>
       <c r="I22" s="5" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="6" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="5" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>250</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J28"/>
   <conditionalFormatting sqref="D2:D24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"已实现"</formula>
@@ -3253,226 +3450,226 @@
   <sheetData>
     <row r="1" spans="1:4" ht="32" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="B2" s="5">
         <v>86</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="B3" s="6">
         <v>86</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="B4" s="5">
         <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="B5" s="6">
         <v>57</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="B6" s="5">
         <v>29</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="B7" s="6">
         <v>57</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="B8" s="5">
         <v>0</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="B11" s="6">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="B12" s="5">
         <v>4</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="B13" s="6">
         <v>57</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -3488,7 +3685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="F10"/>
+  <dimension ref="F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3501,162 +3698,162 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3699,8 +3896,25 @@
         <v>27</v>
       </c>
     </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="8" fitToWidth="1" fitToHeight="0" orientation="landscape"/>
 </worksheet>
@@ -3724,19 +3938,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3744,16 +3958,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3761,16 +3975,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3778,16 +3992,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3795,16 +4009,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>357</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3812,16 +4026,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>361</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3829,16 +4043,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>363</v>
+        <v>394</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3846,16 +4060,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3863,16 +4077,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
